--- a/data/daily_manual_rain_gage_data.xlsx
+++ b/data/daily_manual_rain_gage_data.xlsx
@@ -1142,7 +1142,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4404"/>
+  <dimension ref="A1:E4451"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -50765,7 +50765,6 @@
       <c r="C4402">
         <v>4.6</v>
       </c>
-      <c r="D4402"/>
       <c r="E4402">
         <v>1</v>
       </c>
@@ -50784,12 +50783,571 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4404" spans="1:2">
+    <row r="4404" spans="1:4">
       <c r="A4404" s="7">
         <v>4402</v>
       </c>
       <c r="B4404" s="10">
         <v>46042</v>
+      </c>
+      <c r="C4404">
+        <v>10.6</v>
+      </c>
+      <c r="D4404">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4405" spans="1:4">
+      <c r="A4405" s="7">
+        <v>4403</v>
+      </c>
+      <c r="B4405" s="10">
+        <v>46043</v>
+      </c>
+      <c r="C4405">
+        <v>3.6</v>
+      </c>
+      <c r="D4405">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4406" spans="1:4">
+      <c r="A4406" s="7">
+        <v>4404</v>
+      </c>
+      <c r="B4406" s="10">
+        <v>46044</v>
+      </c>
+      <c r="C4406">
+        <v>8.4</v>
+      </c>
+      <c r="D4406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4407" spans="1:4">
+      <c r="A4407" s="7">
+        <v>4405</v>
+      </c>
+      <c r="B4407" s="10">
+        <v>46045</v>
+      </c>
+      <c r="C4407">
+        <v>0.2</v>
+      </c>
+      <c r="D4407">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4408" spans="1:4">
+      <c r="A4408" s="7">
+        <v>4406</v>
+      </c>
+      <c r="B4408" s="10">
+        <v>46046</v>
+      </c>
+      <c r="C4408">
+        <v>3.8</v>
+      </c>
+      <c r="D4408">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4409" spans="1:4">
+      <c r="A4409" s="7">
+        <v>4407</v>
+      </c>
+      <c r="B4409" s="10">
+        <v>46047</v>
+      </c>
+      <c r="C4409">
+        <v>0.2</v>
+      </c>
+      <c r="D4409">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4410" spans="1:3">
+      <c r="A4410" s="7">
+        <v>4408</v>
+      </c>
+      <c r="B4410" s="10">
+        <v>46048</v>
+      </c>
+      <c r="C4410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4411" spans="1:3">
+      <c r="A4411" s="7">
+        <v>4409</v>
+      </c>
+      <c r="B4411" s="10">
+        <v>46049</v>
+      </c>
+      <c r="C4411">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="4412" spans="1:3">
+      <c r="A4412" s="7">
+        <v>4410</v>
+      </c>
+      <c r="B4412" s="10">
+        <v>46050</v>
+      </c>
+      <c r="C4412">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="4413" spans="1:4">
+      <c r="A4413" s="7">
+        <v>4411</v>
+      </c>
+      <c r="B4413" s="10">
+        <v>46051</v>
+      </c>
+      <c r="C4413">
+        <v>1.2</v>
+      </c>
+      <c r="D4413">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4414" spans="1:3">
+      <c r="A4414" s="7">
+        <v>4412</v>
+      </c>
+      <c r="B4414" s="10">
+        <v>46052</v>
+      </c>
+      <c r="C4414">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4415" spans="1:3">
+      <c r="A4415" s="7">
+        <v>4413</v>
+      </c>
+      <c r="B4415" s="10">
+        <v>46053</v>
+      </c>
+      <c r="C4415">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="4416" spans="1:3">
+      <c r="A4416" s="7">
+        <v>4414</v>
+      </c>
+      <c r="B4416" s="10">
+        <v>46054</v>
+      </c>
+      <c r="C4416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4417" spans="1:3">
+      <c r="A4417" s="7">
+        <v>4415</v>
+      </c>
+      <c r="B4417" s="10">
+        <v>46055</v>
+      </c>
+      <c r="C4417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4418" spans="1:3">
+      <c r="A4418" s="7">
+        <v>4416</v>
+      </c>
+      <c r="B4418" s="10">
+        <v>46056</v>
+      </c>
+      <c r="C4418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4419" spans="1:3">
+      <c r="A4419" s="7">
+        <v>4417</v>
+      </c>
+      <c r="B4419" s="10">
+        <v>46057</v>
+      </c>
+      <c r="C4419">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4420" spans="1:3">
+      <c r="A4420" s="7">
+        <v>4418</v>
+      </c>
+      <c r="B4420" s="10">
+        <v>46058</v>
+      </c>
+      <c r="C4420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4421" spans="1:3">
+      <c r="A4421" s="7">
+        <v>4419</v>
+      </c>
+      <c r="B4421" s="10">
+        <v>46059</v>
+      </c>
+      <c r="C4421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4422" spans="1:3">
+      <c r="A4422" s="7">
+        <v>4420</v>
+      </c>
+      <c r="B4422" s="10">
+        <v>46060</v>
+      </c>
+      <c r="C4422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4423" spans="1:4">
+      <c r="A4423" s="7">
+        <v>4421</v>
+      </c>
+      <c r="B4423" s="10">
+        <v>46061</v>
+      </c>
+      <c r="C4423">
+        <v>2.6</v>
+      </c>
+      <c r="D4423">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4424" spans="1:3">
+      <c r="A4424" s="7">
+        <v>4422</v>
+      </c>
+      <c r="B4424" s="10">
+        <v>46062</v>
+      </c>
+      <c r="C4424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4425" spans="1:3">
+      <c r="A4425" s="7">
+        <v>4423</v>
+      </c>
+      <c r="B4425" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C4425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4426" spans="1:3">
+      <c r="A4426" s="7">
+        <v>4424</v>
+      </c>
+      <c r="B4426" s="10">
+        <v>46064</v>
+      </c>
+      <c r="C4426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4427" spans="1:3">
+      <c r="A4427" s="7">
+        <v>4425</v>
+      </c>
+      <c r="B4427" s="10">
+        <v>46065</v>
+      </c>
+      <c r="C4427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4428" spans="1:4">
+      <c r="A4428" s="7">
+        <v>4426</v>
+      </c>
+      <c r="B4428" s="10">
+        <v>46066</v>
+      </c>
+      <c r="C4428">
+        <v>4</v>
+      </c>
+      <c r="D4428">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4429" spans="1:3">
+      <c r="A4429" s="7">
+        <v>4427</v>
+      </c>
+      <c r="B4429" s="10">
+        <v>46067</v>
+      </c>
+      <c r="C4429">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="4430" spans="1:3">
+      <c r="A4430" s="7">
+        <v>4428</v>
+      </c>
+      <c r="B4430" s="10">
+        <v>46068</v>
+      </c>
+      <c r="C4430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4431" spans="1:3">
+      <c r="A4431" s="7">
+        <v>4429</v>
+      </c>
+      <c r="B4431" s="10">
+        <v>46069</v>
+      </c>
+      <c r="C4431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4432" spans="1:3">
+      <c r="A4432" s="7">
+        <v>4430</v>
+      </c>
+      <c r="B4432" s="10">
+        <v>46070</v>
+      </c>
+      <c r="C4432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4433" spans="1:3">
+      <c r="A4433" s="7">
+        <v>4431</v>
+      </c>
+      <c r="B4433" s="10">
+        <v>46071</v>
+      </c>
+      <c r="C4433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4434" spans="1:3">
+      <c r="A4434" s="7">
+        <v>4432</v>
+      </c>
+      <c r="B4434" s="10">
+        <v>46072</v>
+      </c>
+      <c r="C4434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4435" spans="1:3">
+      <c r="A4435" s="7">
+        <v>4433</v>
+      </c>
+      <c r="B4435" s="10">
+        <v>46073</v>
+      </c>
+      <c r="C4435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4436" spans="1:3">
+      <c r="A4436" s="7">
+        <v>4434</v>
+      </c>
+      <c r="B4436" s="10">
+        <v>46074</v>
+      </c>
+      <c r="C4436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4437" spans="1:3">
+      <c r="A4437" s="7">
+        <v>4435</v>
+      </c>
+      <c r="B4437" s="10">
+        <v>46075</v>
+      </c>
+      <c r="C4437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4438" spans="1:3">
+      <c r="A4438" s="7">
+        <v>4436</v>
+      </c>
+      <c r="B4438" s="10">
+        <v>46076</v>
+      </c>
+      <c r="C4438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4439" spans="1:4">
+      <c r="A4439" s="7">
+        <v>4437</v>
+      </c>
+      <c r="B4439" s="10">
+        <v>46077</v>
+      </c>
+      <c r="C4439">
+        <v>0.2</v>
+      </c>
+      <c r="D4439">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4440" spans="1:3">
+      <c r="A4440" s="7">
+        <v>4438</v>
+      </c>
+      <c r="B4440" s="10">
+        <v>46078</v>
+      </c>
+      <c r="C4440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4441" spans="1:3">
+      <c r="A4441" s="7">
+        <v>4439</v>
+      </c>
+      <c r="B4441" s="10">
+        <v>46079</v>
+      </c>
+      <c r="C4441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4442" spans="1:3">
+      <c r="A4442" s="7">
+        <v>4440</v>
+      </c>
+      <c r="B4442" s="10">
+        <v>46080</v>
+      </c>
+      <c r="C4442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4443" spans="1:3">
+      <c r="A4443" s="7">
+        <v>4441</v>
+      </c>
+      <c r="B4443" s="10">
+        <v>46081</v>
+      </c>
+      <c r="C4443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4444" spans="1:3">
+      <c r="A4444" s="7">
+        <v>4442</v>
+      </c>
+      <c r="B4444" s="10">
+        <v>46082</v>
+      </c>
+      <c r="C4444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4445" spans="1:3">
+      <c r="A4445" s="7">
+        <v>4443</v>
+      </c>
+      <c r="B4445" s="10">
+        <v>46083</v>
+      </c>
+      <c r="C4445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4446" spans="1:3">
+      <c r="A4446" s="7">
+        <v>4444</v>
+      </c>
+      <c r="B4446" s="10">
+        <v>46084</v>
+      </c>
+      <c r="C4446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4447" spans="1:3">
+      <c r="A4447" s="7">
+        <v>4445</v>
+      </c>
+      <c r="B4447" s="10">
+        <v>46085</v>
+      </c>
+      <c r="C4447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4448" spans="1:4">
+      <c r="A4448" s="7">
+        <v>4446</v>
+      </c>
+      <c r="B4448" s="10">
+        <v>46086</v>
+      </c>
+      <c r="C4448">
+        <v>9.4</v>
+      </c>
+      <c r="D4448">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4449" spans="1:4">
+      <c r="A4449" s="7">
+        <v>4447</v>
+      </c>
+      <c r="B4449" s="10">
+        <v>46087</v>
+      </c>
+      <c r="C4449">
+        <v>25</v>
+      </c>
+      <c r="D4449">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4450" spans="1:4">
+      <c r="A4450" s="7">
+        <v>4448</v>
+      </c>
+      <c r="B4450" s="10">
+        <v>46088</v>
+      </c>
+      <c r="C4450">
+        <v>12.4</v>
+      </c>
+      <c r="D4450">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4451" spans="1:3">
+      <c r="A4451" s="7">
+        <v>4449</v>
+      </c>
+      <c r="B4451" s="10">
+        <v>46089</v>
+      </c>
+      <c r="C4451">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily_manual_rain_gage_data.xlsx
+++ b/data/daily_manual_rain_gage_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eiven\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eiven\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F921B943-2BBE-40A8-A51F-6BF513C8F77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434B4394-30FD-4D99-9054-3DBCA633B0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -145,7 +145,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -250,7 +250,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -531,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4470"/>
+  <dimension ref="A1:E4472"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -50946,6 +50946,28 @@
       </c>
       <c r="C4470">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4471" spans="1:3">
+      <c r="A4471" s="7">
+        <v>4469</v>
+      </c>
+      <c r="B4471" s="10">
+        <v>46109</v>
+      </c>
+      <c r="C4471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4472" spans="1:3">
+      <c r="A4472" s="7">
+        <v>4470</v>
+      </c>
+      <c r="B4472" s="10">
+        <v>46110</v>
+      </c>
+      <c r="C4472">
+        <v>35.200000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily_manual_rain_gage_data.xlsx
+++ b/data/daily_manual_rain_gage_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eiven\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eiven\Desktop\Eiven\git\app-secar_meteo_data\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434B4394-30FD-4D99-9054-3DBCA633B0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B11F6A-88C0-482F-83A5-C32C5AF86536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -531,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4472"/>
+  <dimension ref="A1:E4476"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -50967,7 +50967,51 @@
         <v>46110</v>
       </c>
       <c r="C4472">
-        <v>35.200000000000003</v>
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="4473" spans="1:3">
+      <c r="A4473" s="7">
+        <v>4471</v>
+      </c>
+      <c r="B4473" s="10">
+        <v>46111</v>
+      </c>
+      <c r="C4473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4474" spans="1:3">
+      <c r="A4474" s="7">
+        <v>4472</v>
+      </c>
+      <c r="B4474" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C4474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4475" spans="1:3">
+      <c r="A4475" s="7">
+        <v>4473</v>
+      </c>
+      <c r="B4475" s="10">
+        <v>46113</v>
+      </c>
+      <c r="C4475">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4476" spans="1:3">
+      <c r="A4476" s="7">
+        <v>4474</v>
+      </c>
+      <c r="B4476" s="10">
+        <v>46114</v>
+      </c>
+      <c r="C4476">
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily_manual_rain_gage_data.xlsx
+++ b/data/daily_manual_rain_gage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eiven\Desktop\Eiven\git\app-secar_meteo_data\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B11F6A-88C0-482F-83A5-C32C5AF86536}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42009865-549F-4109-9919-8A2470EF441B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -531,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4476"/>
+  <dimension ref="A1:E4505"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -51012,6 +51012,331 @@
       </c>
       <c r="C4476">
         <v>2.4</v>
+      </c>
+    </row>
+    <row r="4477" spans="1:3">
+      <c r="A4477" s="7">
+        <v>4475</v>
+      </c>
+      <c r="B4477" s="10">
+        <v>46115</v>
+      </c>
+      <c r="C4477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4478" spans="1:3">
+      <c r="A4478" s="7">
+        <v>4476</v>
+      </c>
+      <c r="B4478" s="10">
+        <v>46116</v>
+      </c>
+      <c r="C4478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4479" spans="1:3">
+      <c r="A4479" s="7">
+        <v>4477</v>
+      </c>
+      <c r="B4479" s="10">
+        <v>46117</v>
+      </c>
+      <c r="C4479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4480" spans="1:3">
+      <c r="A4480" s="7">
+        <v>4478</v>
+      </c>
+      <c r="B4480" s="10">
+        <v>46118</v>
+      </c>
+      <c r="C4480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4481" spans="1:4">
+      <c r="A4481" s="7">
+        <v>4479</v>
+      </c>
+      <c r="B4481" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C4481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4482" spans="1:4">
+      <c r="A4482" s="7">
+        <v>4480</v>
+      </c>
+      <c r="B4482" s="10">
+        <v>46120</v>
+      </c>
+      <c r="C4482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4483" spans="1:4">
+      <c r="A4483" s="7">
+        <v>4481</v>
+      </c>
+      <c r="B4483" s="10">
+        <v>46121</v>
+      </c>
+      <c r="C4483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4484" spans="1:4">
+      <c r="A4484" s="7">
+        <v>4482</v>
+      </c>
+      <c r="B4484" s="10">
+        <v>46122</v>
+      </c>
+      <c r="C4484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4485" spans="1:4">
+      <c r="A4485" s="7">
+        <v>4483</v>
+      </c>
+      <c r="B4485" s="10">
+        <v>46123</v>
+      </c>
+      <c r="C4485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4486" spans="1:4">
+      <c r="A4486" s="7">
+        <v>4484</v>
+      </c>
+      <c r="B4486" s="10">
+        <v>46124</v>
+      </c>
+      <c r="C4486">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D4486">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4487" spans="1:4">
+      <c r="A4487" s="7">
+        <v>4485</v>
+      </c>
+      <c r="B4487" s="10">
+        <v>46125</v>
+      </c>
+      <c r="C4487">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D4487">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4488" spans="1:4">
+      <c r="A4488" s="7">
+        <v>4486</v>
+      </c>
+      <c r="B4488" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C4488">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4489" spans="1:4">
+      <c r="A4489" s="7">
+        <v>4487</v>
+      </c>
+      <c r="B4489" s="10">
+        <v>46127</v>
+      </c>
+      <c r="C4489">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4490" spans="1:4">
+      <c r="A4490" s="7">
+        <v>4488</v>
+      </c>
+      <c r="B4490" s="10">
+        <v>46128</v>
+      </c>
+      <c r="C4490">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4491" spans="1:4">
+      <c r="A4491" s="7">
+        <v>4489</v>
+      </c>
+      <c r="B4491" s="10">
+        <v>46129</v>
+      </c>
+      <c r="C4491">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4492" spans="1:4">
+      <c r="A4492" s="7">
+        <v>4490</v>
+      </c>
+      <c r="B4492" s="10">
+        <v>46130</v>
+      </c>
+      <c r="C4492">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4493" spans="1:4">
+      <c r="A4493" s="7">
+        <v>4491</v>
+      </c>
+      <c r="B4493" s="10">
+        <v>46131</v>
+      </c>
+      <c r="C4493">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4494" spans="1:4">
+      <c r="A4494" s="7">
+        <v>4492</v>
+      </c>
+      <c r="B4494" s="10">
+        <v>46132</v>
+      </c>
+      <c r="C4494">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4495" spans="1:4">
+      <c r="A4495" s="7">
+        <v>4493</v>
+      </c>
+      <c r="B4495" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C4495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4496" spans="1:4">
+      <c r="A4496" s="7">
+        <v>4494</v>
+      </c>
+      <c r="B4496" s="10">
+        <v>46134</v>
+      </c>
+      <c r="C4496">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4497" spans="1:3">
+      <c r="A4497" s="7">
+        <v>4495</v>
+      </c>
+      <c r="B4497" s="10">
+        <v>46135</v>
+      </c>
+      <c r="C4497">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4498" spans="1:3">
+      <c r="A4498" s="7">
+        <v>4496</v>
+      </c>
+      <c r="B4498" s="10">
+        <v>46136</v>
+      </c>
+      <c r="C4498">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4499" spans="1:3">
+      <c r="A4499" s="7">
+        <v>4497</v>
+      </c>
+      <c r="B4499" s="10">
+        <v>46137</v>
+      </c>
+      <c r="C4499">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4500" spans="1:3">
+      <c r="A4500" s="7">
+        <v>4498</v>
+      </c>
+      <c r="B4500" s="10">
+        <v>46138</v>
+      </c>
+      <c r="C4500">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4501" spans="1:3">
+      <c r="A4501" s="7">
+        <v>4499</v>
+      </c>
+      <c r="B4501" s="10">
+        <v>46139</v>
+      </c>
+      <c r="C4501">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4502" spans="1:3">
+      <c r="A4502" s="7">
+        <v>4500</v>
+      </c>
+      <c r="B4502" s="10">
+        <v>46140</v>
+      </c>
+      <c r="C4502">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4503" spans="1:3">
+      <c r="A4503" s="7">
+        <v>4501</v>
+      </c>
+      <c r="B4503" s="10">
+        <v>46141</v>
+      </c>
+      <c r="C4503">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4504" spans="1:3">
+      <c r="A4504" s="7">
+        <v>4502</v>
+      </c>
+      <c r="B4504" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C4504">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4505" spans="1:3">
+      <c r="A4505" s="7">
+        <v>4503</v>
+      </c>
+      <c r="B4505" s="10">
+        <v>46143</v>
+      </c>
+      <c r="C4505">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/daily_manual_rain_gage_data.xlsx
+++ b/data/daily_manual_rain_gage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eiven\Desktop\Eiven\git\app-secar_meteo_data\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42009865-549F-4109-9919-8A2470EF441B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA36985-F714-493E-9D24-4CBD3CF5A37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manual rain gage data" sheetId="1" r:id="rId1"/>
@@ -531,12 +531,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4505"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.5"/>
+  <dimension ref="A1:E4521"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="9.1796875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51240,7 +51240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4497" spans="1:3">
+    <row r="4497" spans="1:5">
       <c r="A4497" s="7">
         <v>4495</v>
       </c>
@@ -51251,7 +51251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4498" spans="1:3">
+    <row r="4498" spans="1:5">
       <c r="A4498" s="7">
         <v>4496</v>
       </c>
@@ -51262,7 +51262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4499" spans="1:3">
+    <row r="4499" spans="1:5">
       <c r="A4499" s="7">
         <v>4497</v>
       </c>
@@ -51273,7 +51273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4500" spans="1:3">
+    <row r="4500" spans="1:5">
       <c r="A4500" s="7">
         <v>4498</v>
       </c>
@@ -51284,7 +51284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4501" spans="1:3">
+    <row r="4501" spans="1:5">
       <c r="A4501" s="7">
         <v>4499</v>
       </c>
@@ -51295,7 +51295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4502" spans="1:3">
+    <row r="4502" spans="1:5">
       <c r="A4502" s="7">
         <v>4500</v>
       </c>
@@ -51306,7 +51306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4503" spans="1:3">
+    <row r="4503" spans="1:5">
       <c r="A4503" s="7">
         <v>4501</v>
       </c>
@@ -51317,7 +51317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4504" spans="1:3">
+    <row r="4504" spans="1:5">
       <c r="A4504" s="7">
         <v>4502</v>
       </c>
@@ -51328,7 +51328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4505" spans="1:3">
+    <row r="4505" spans="1:5">
       <c r="A4505" s="7">
         <v>4503</v>
       </c>
@@ -51336,6 +51336,186 @@
         <v>46143</v>
       </c>
       <c r="C4505">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4506" spans="1:5">
+      <c r="A4506" s="7">
+        <v>4504</v>
+      </c>
+      <c r="B4506" s="10">
+        <v>46144</v>
+      </c>
+      <c r="C4506">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4507" spans="1:5">
+      <c r="A4507" s="7">
+        <v>4505</v>
+      </c>
+      <c r="B4507" s="10">
+        <v>46145</v>
+      </c>
+      <c r="C4507">
+        <v>12</v>
+      </c>
+      <c r="E4507">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4508" spans="1:5">
+      <c r="A4508" s="7">
+        <v>4506</v>
+      </c>
+      <c r="B4508" s="10">
+        <v>46146</v>
+      </c>
+      <c r="C4508">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4509" spans="1:5">
+      <c r="A4509" s="7">
+        <v>4507</v>
+      </c>
+      <c r="B4509" s="10">
+        <v>46147</v>
+      </c>
+      <c r="C4509">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4510" spans="1:5">
+      <c r="A4510" s="7">
+        <v>4508</v>
+      </c>
+      <c r="B4510" s="10">
+        <v>46148</v>
+      </c>
+      <c r="C4510">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4511" spans="1:5">
+      <c r="A4511" s="7">
+        <v>4509</v>
+      </c>
+      <c r="B4511" s="10">
+        <v>46149</v>
+      </c>
+      <c r="C4511">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="4512" spans="1:5">
+      <c r="A4512" s="7">
+        <v>4510</v>
+      </c>
+      <c r="B4512" s="10">
+        <v>46150</v>
+      </c>
+      <c r="C4512">
+        <f>12.8-C4511</f>
+        <v>5.6000000000000005</v>
+      </c>
+    </row>
+    <row r="4513" spans="1:3">
+      <c r="A4513" s="7">
+        <v>4511</v>
+      </c>
+      <c r="B4513" s="10">
+        <v>46151</v>
+      </c>
+      <c r="C4513">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="4514" spans="1:3">
+      <c r="A4514" s="7">
+        <v>4512</v>
+      </c>
+      <c r="B4514" s="10">
+        <v>46152</v>
+      </c>
+      <c r="C4514">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4515" spans="1:3">
+      <c r="A4515" s="7">
+        <v>4513</v>
+      </c>
+      <c r="B4515" s="10">
+        <v>46153</v>
+      </c>
+      <c r="C4515">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4516" spans="1:3">
+      <c r="A4516" s="7">
+        <v>4514</v>
+      </c>
+      <c r="B4516" s="10">
+        <v>46154</v>
+      </c>
+      <c r="C4516">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4517" spans="1:3">
+      <c r="A4517" s="7">
+        <v>4515</v>
+      </c>
+      <c r="B4517" s="10">
+        <v>46155</v>
+      </c>
+      <c r="C4517">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4518" spans="1:3">
+      <c r="A4518" s="7">
+        <v>4516</v>
+      </c>
+      <c r="B4518" s="10">
+        <v>46156</v>
+      </c>
+      <c r="C4518">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="4519" spans="1:3">
+      <c r="A4519" s="7">
+        <v>4517</v>
+      </c>
+      <c r="B4519" s="10">
+        <v>46157</v>
+      </c>
+      <c r="C4519">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="4520" spans="1:3">
+      <c r="A4520" s="7">
+        <v>4518</v>
+      </c>
+      <c r="B4520" s="10">
+        <v>46158</v>
+      </c>
+      <c r="C4520">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4521" spans="1:3">
+      <c r="A4521" s="7">
+        <v>4519</v>
+      </c>
+      <c r="B4521" s="10">
+        <v>46159</v>
+      </c>
+      <c r="C4521">
         <v>0</v>
       </c>
     </row>
@@ -51347,14 +51527,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="43" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="42.95" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.453125" customWidth="1"/>
-    <col min="2" max="2" width="13.6328125" customWidth="1"/>
-    <col min="3" max="3" width="17.08984375" customWidth="1"/>
-    <col min="4" max="4" width="18.90625" customWidth="1"/>
-    <col min="5" max="5" width="37.08984375" customWidth="1"/>
-    <col min="6" max="6" width="34.6328125" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" customWidth="1"/>
+    <col min="5" max="5" width="37.140625" customWidth="1"/>
+    <col min="6" max="6" width="34.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1">
@@ -51391,7 +51571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="43" customHeight="1">
+    <row r="3" spans="1:5" ht="42.95" customHeight="1">
       <c r="A3" s="2">
         <v>41753</v>
       </c>
@@ -51408,7 +51588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="43" customHeight="1">
+    <row r="4" spans="1:5" ht="42.95" customHeight="1">
       <c r="A4" s="2">
         <v>42001</v>
       </c>
@@ -51425,7 +51605,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="43" customHeight="1">
+    <row r="5" spans="1:5" ht="42.95" customHeight="1">
       <c r="A5" s="2">
         <v>42002</v>
       </c>
@@ -51442,7 +51622,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="43" customHeight="1">
+    <row r="6" spans="1:5" ht="42.95" customHeight="1">
       <c r="A6" s="2">
         <v>41643</v>
       </c>
@@ -51459,7 +51639,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="43" customHeight="1">
+    <row r="7" spans="1:5" ht="42.95" customHeight="1">
       <c r="A7" s="2">
         <v>41668</v>
       </c>
@@ -51476,7 +51656,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="43" customHeight="1">
+    <row r="8" spans="1:5" ht="42.95" customHeight="1">
       <c r="A8" s="2">
         <v>41675</v>
       </c>
@@ -51490,7 +51670,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="43" customHeight="1">
+    <row r="9" spans="1:5" ht="42.95" customHeight="1">
       <c r="A9" s="2">
         <v>42234</v>
       </c>
@@ -51504,7 +51684,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="43" customHeight="1">
+    <row r="10" spans="1:5" ht="42.95" customHeight="1">
       <c r="A10" s="2">
         <v>42372</v>
       </c>
@@ -51518,7 +51698,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="43" customHeight="1">
+    <row r="11" spans="1:5" ht="42.95" customHeight="1">
       <c r="A11" s="2">
         <v>42407</v>
       </c>
@@ -51532,7 +51712,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="43" customHeight="1">
+    <row r="12" spans="1:5" ht="42.95" customHeight="1">
       <c r="A12" s="2">
         <v>42415</v>
       </c>
@@ -51546,7 +51726,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="43" customHeight="1">
+    <row r="13" spans="1:5" ht="42.95" customHeight="1">
       <c r="A13" s="2">
         <v>42427</v>
       </c>
@@ -51560,7 +51740,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="43" customHeight="1">
+    <row r="14" spans="1:5" ht="42.95" customHeight="1">
       <c r="A14" s="2">
         <v>42439</v>
       </c>
@@ -51574,7 +51754,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="43" customHeight="1">
+    <row r="15" spans="1:5" ht="42.95" customHeight="1">
       <c r="A15" s="2">
         <v>42444</v>
       </c>
@@ -51588,7 +51768,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="43" customHeight="1">
+    <row r="16" spans="1:5" ht="42.95" customHeight="1">
       <c r="A16" s="2">
         <v>42448</v>
       </c>
@@ -51602,7 +51782,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="43" customHeight="1">
+    <row r="17" spans="1:4" ht="42.95" customHeight="1">
       <c r="A17" s="2">
         <v>42468</v>
       </c>
@@ -51616,7 +51796,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="43" customHeight="1">
+    <row r="18" spans="1:4" ht="42.95" customHeight="1">
       <c r="A18" s="2">
         <v>42480</v>
       </c>
@@ -51630,7 +51810,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="43" customHeight="1">
+    <row r="19" spans="1:4" ht="42.95" customHeight="1">
       <c r="A19" s="2">
         <v>42491</v>
       </c>
@@ -51644,7 +51824,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="43" customHeight="1">
+    <row r="20" spans="1:4" ht="42.95" customHeight="1">
       <c r="A20" s="2">
         <v>42549</v>
       </c>
@@ -51658,7 +51838,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="43" customHeight="1">
+    <row r="21" spans="1:4" ht="42.95" customHeight="1">
       <c r="A21" s="2">
         <v>42550</v>
       </c>
@@ -51672,7 +51852,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="43" customHeight="1">
+    <row r="22" spans="1:4" ht="42.95" customHeight="1">
       <c r="A22" s="2">
         <v>43158</v>
       </c>
@@ -51686,7 +51866,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="43" customHeight="1">
+    <row r="23" spans="1:4" ht="42.95" customHeight="1">
       <c r="A23" s="2">
         <v>43159</v>
       </c>
@@ -51700,7 +51880,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="43" customHeight="1">
+    <row r="24" spans="1:4" ht="42.95" customHeight="1">
       <c r="A24" s="2">
         <v>43160</v>
       </c>
@@ -51714,7 +51894,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="43" customHeight="1">
+    <row r="25" spans="1:4" ht="42.95" customHeight="1">
       <c r="A25" s="2">
         <v>43161</v>
       </c>
@@ -51728,7 +51908,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="43" customHeight="1">
+    <row r="26" spans="1:4" ht="42.95" customHeight="1">
       <c r="A26" s="2">
         <v>43358</v>
       </c>
@@ -51742,7 +51922,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="43" customHeight="1">
+    <row r="27" spans="1:4" ht="42.95" customHeight="1">
       <c r="A27" s="2">
         <v>43360</v>
       </c>
@@ -51756,7 +51936,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="43" customHeight="1">
+    <row r="28" spans="1:4" ht="42.95" customHeight="1">
       <c r="A28" s="2">
         <v>43413</v>
       </c>
@@ -51770,7 +51950,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="43" customHeight="1">
+    <row r="29" spans="1:4" ht="42.95" customHeight="1">
       <c r="A29" s="2">
         <v>43418</v>
       </c>
@@ -51784,7 +51964,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="43" customHeight="1">
+    <row r="30" spans="1:4" ht="42.95" customHeight="1">
       <c r="A30" s="2">
         <v>43430</v>
       </c>
@@ -51798,7 +51978,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="43" customHeight="1">
+    <row r="31" spans="1:4" ht="42.95" customHeight="1">
       <c r="A31" s="2">
         <v>43654</v>
       </c>

--- a/data/daily_manual_rain_gage_data.xlsx
+++ b/data/daily_manual_rain_gage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eiven\Desktop\Eiven\git\app-secar_meteo_data\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA36985-F714-493E-9D24-4CBD3CF5A37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD085F7-92C1-467F-B47B-4BE6CF306DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -531,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4521"/>
+  <dimension ref="A1:E4554"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -51516,6 +51516,369 @@
         <v>46159</v>
       </c>
       <c r="C4521">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4522" spans="1:3">
+      <c r="A4522" s="7">
+        <v>4520</v>
+      </c>
+      <c r="B4522" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C4522">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4523" spans="1:3">
+      <c r="A4523" s="7">
+        <v>4521</v>
+      </c>
+      <c r="B4523" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C4523">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4524" spans="1:3">
+      <c r="A4524" s="7">
+        <v>4522</v>
+      </c>
+      <c r="B4524" s="10">
+        <v>46162</v>
+      </c>
+      <c r="C4524">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4525" spans="1:3">
+      <c r="A4525" s="7">
+        <v>4523</v>
+      </c>
+      <c r="B4525" s="10">
+        <v>46163</v>
+      </c>
+      <c r="C4525">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4526" spans="1:3">
+      <c r="A4526" s="7">
+        <v>4524</v>
+      </c>
+      <c r="B4526" s="10">
+        <v>46164</v>
+      </c>
+      <c r="C4526">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4527" spans="1:3">
+      <c r="A4527" s="7">
+        <v>4525</v>
+      </c>
+      <c r="B4527" s="10">
+        <v>46165</v>
+      </c>
+      <c r="C4527">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4528" spans="1:3">
+      <c r="A4528" s="7">
+        <v>4526</v>
+      </c>
+      <c r="B4528" s="10">
+        <v>46166</v>
+      </c>
+      <c r="C4528">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4529" spans="1:3">
+      <c r="A4529" s="7">
+        <v>4527</v>
+      </c>
+      <c r="B4529" s="10">
+        <v>46167</v>
+      </c>
+      <c r="C4529">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4530" spans="1:3">
+      <c r="A4530" s="7">
+        <v>4528</v>
+      </c>
+      <c r="B4530" s="10">
+        <v>46168</v>
+      </c>
+      <c r="C4530">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4531" spans="1:3">
+      <c r="A4531" s="7">
+        <v>4529</v>
+      </c>
+      <c r="B4531" s="10">
+        <v>46169</v>
+      </c>
+      <c r="C4531">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4532" spans="1:3">
+      <c r="A4532" s="7">
+        <v>4530</v>
+      </c>
+      <c r="B4532" s="10">
+        <v>46170</v>
+      </c>
+      <c r="C4532">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4533" spans="1:3">
+      <c r="A4533" s="7">
+        <v>4531</v>
+      </c>
+      <c r="B4533" s="10">
+        <v>46171</v>
+      </c>
+      <c r="C4533">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4534" spans="1:3">
+      <c r="A4534" s="7">
+        <v>4532</v>
+      </c>
+      <c r="B4534" s="10">
+        <v>46172</v>
+      </c>
+      <c r="C4534">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4535" spans="1:3">
+      <c r="A4535" s="7">
+        <v>4533</v>
+      </c>
+      <c r="B4535" s="10">
+        <v>46173</v>
+      </c>
+      <c r="C4535">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4536" spans="1:3">
+      <c r="A4536" s="7">
+        <v>4534</v>
+      </c>
+      <c r="B4536" s="10">
+        <v>46174</v>
+      </c>
+      <c r="C4536">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4537" spans="1:3">
+      <c r="A4537" s="7">
+        <v>4535</v>
+      </c>
+      <c r="B4537" s="10">
+        <v>46175</v>
+      </c>
+      <c r="C4537">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4538" spans="1:3">
+      <c r="A4538" s="7">
+        <v>4536</v>
+      </c>
+      <c r="B4538" s="10">
+        <v>46176</v>
+      </c>
+      <c r="C4538">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4539" spans="1:3">
+      <c r="A4539" s="7">
+        <v>4537</v>
+      </c>
+      <c r="B4539" s="10">
+        <v>46177</v>
+      </c>
+      <c r="C4539">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4540" spans="1:3">
+      <c r="A4540" s="7">
+        <v>4538</v>
+      </c>
+      <c r="B4540" s="10">
+        <v>46178</v>
+      </c>
+      <c r="C4540">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4541" spans="1:3">
+      <c r="A4541" s="7">
+        <v>4539</v>
+      </c>
+      <c r="B4541" s="10">
+        <v>46179</v>
+      </c>
+      <c r="C4541">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4542" spans="1:3">
+      <c r="A4542" s="7">
+        <v>4540</v>
+      </c>
+      <c r="B4542" s="10">
+        <v>46180</v>
+      </c>
+      <c r="C4542">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4543" spans="1:3">
+      <c r="A4543" s="7">
+        <v>4541</v>
+      </c>
+      <c r="B4543" s="10">
+        <v>46181</v>
+      </c>
+      <c r="C4543">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4544" spans="1:3">
+      <c r="A4544" s="7">
+        <v>4542</v>
+      </c>
+      <c r="B4544" s="10">
+        <v>46182</v>
+      </c>
+      <c r="C4544">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4545" spans="1:3">
+      <c r="A4545" s="7">
+        <v>4543</v>
+      </c>
+      <c r="B4545" s="10">
+        <v>46183</v>
+      </c>
+      <c r="C4545">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4546" spans="1:3">
+      <c r="A4546" s="7">
+        <v>4544</v>
+      </c>
+      <c r="B4546" s="10">
+        <v>46184</v>
+      </c>
+      <c r="C4546">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4547" spans="1:3">
+      <c r="A4547" s="7">
+        <v>4545</v>
+      </c>
+      <c r="B4547" s="10">
+        <v>46185</v>
+      </c>
+      <c r="C4547">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4548" spans="1:3">
+      <c r="A4548" s="7">
+        <v>4546</v>
+      </c>
+      <c r="B4548" s="10">
+        <v>46186</v>
+      </c>
+      <c r="C4548">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4549" spans="1:3">
+      <c r="A4549" s="7">
+        <v>4547</v>
+      </c>
+      <c r="B4549" s="10">
+        <v>46187</v>
+      </c>
+      <c r="C4549">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4550" spans="1:3">
+      <c r="A4550" s="7">
+        <v>4548</v>
+      </c>
+      <c r="B4550" s="10">
+        <v>46188</v>
+      </c>
+      <c r="C4550">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4551" spans="1:3">
+      <c r="A4551" s="7">
+        <v>4549</v>
+      </c>
+      <c r="B4551" s="10">
+        <v>46189</v>
+      </c>
+      <c r="C4551">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4552" spans="1:3">
+      <c r="A4552" s="7">
+        <v>4550</v>
+      </c>
+      <c r="B4552" s="10">
+        <v>46190</v>
+      </c>
+      <c r="C4552">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4553" spans="1:3">
+      <c r="A4553" s="7">
+        <v>4551</v>
+      </c>
+      <c r="B4553" s="10">
+        <v>46191</v>
+      </c>
+      <c r="C4553">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4554" spans="1:3">
+      <c r="A4554" s="7">
+        <v>4552</v>
+      </c>
+      <c r="B4554" s="10">
+        <v>46192</v>
+      </c>
+      <c r="C4554">
         <v>0</v>
       </c>
     </row>

--- a/data/daily_manual_rain_gage_data.xlsx
+++ b/data/daily_manual_rain_gage_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eiven\Desktop\Eiven\git\app-secar_meteo_data\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eiven\O2 Cloud\git\app-secar_meteo_data\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD085F7-92C1-467F-B47B-4BE6CF306DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC7B50B-F022-4715-B256-6BF0393E6406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manual rain gage data" sheetId="1" r:id="rId1"/>
@@ -531,12 +531,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4554"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
+  <dimension ref="A1:E4596"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="9.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -51879,6 +51879,474 @@
         <v>46192</v>
       </c>
       <c r="C4554">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4555" spans="1:3">
+      <c r="A4555" s="7">
+        <v>4553</v>
+      </c>
+      <c r="B4555" s="10">
+        <v>46193</v>
+      </c>
+      <c r="C4555">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4556" spans="1:3">
+      <c r="A4556" s="7">
+        <v>4554</v>
+      </c>
+      <c r="B4556" s="10">
+        <v>46194</v>
+      </c>
+      <c r="C4556">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4557" spans="1:3">
+      <c r="A4557" s="7">
+        <v>4555</v>
+      </c>
+      <c r="B4557" s="10">
+        <v>46195</v>
+      </c>
+      <c r="C4557">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4558" spans="1:3">
+      <c r="A4558" s="7">
+        <v>4556</v>
+      </c>
+      <c r="B4558" s="10">
+        <v>46196</v>
+      </c>
+      <c r="C4558">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4559" spans="1:3">
+      <c r="A4559" s="7">
+        <v>4557</v>
+      </c>
+      <c r="B4559" s="10">
+        <v>46197</v>
+      </c>
+      <c r="C4559">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4560" spans="1:3">
+      <c r="A4560" s="7">
+        <v>4558</v>
+      </c>
+      <c r="B4560" s="10">
+        <v>46198</v>
+      </c>
+      <c r="C4560">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4561" spans="1:3">
+      <c r="A4561" s="7">
+        <v>4559</v>
+      </c>
+      <c r="B4561" s="10">
+        <v>46199</v>
+      </c>
+      <c r="C4561">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4562" spans="1:3">
+      <c r="A4562" s="7">
+        <v>4560</v>
+      </c>
+      <c r="B4562" s="10">
+        <v>46200</v>
+      </c>
+      <c r="C4562">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4563" spans="1:3">
+      <c r="A4563" s="7">
+        <v>4561</v>
+      </c>
+      <c r="B4563" s="10">
+        <v>46201</v>
+      </c>
+      <c r="C4563">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4564" spans="1:3">
+      <c r="A4564" s="7">
+        <v>4562</v>
+      </c>
+      <c r="B4564" s="10">
+        <v>46202</v>
+      </c>
+      <c r="C4564">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4565" spans="1:3">
+      <c r="A4565" s="7">
+        <v>4563</v>
+      </c>
+      <c r="B4565" s="10">
+        <v>46203</v>
+      </c>
+      <c r="C4565">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4566" spans="1:3">
+      <c r="A4566" s="7">
+        <v>4564</v>
+      </c>
+      <c r="B4566" s="10">
+        <v>46204</v>
+      </c>
+      <c r="C4566">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4567" spans="1:3">
+      <c r="A4567" s="7">
+        <v>4565</v>
+      </c>
+      <c r="B4567" s="10">
+        <v>46205</v>
+      </c>
+      <c r="C4567">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4568" spans="1:3">
+      <c r="A4568" s="7">
+        <v>4566</v>
+      </c>
+      <c r="B4568" s="10">
+        <v>46206</v>
+      </c>
+      <c r="C4568">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4569" spans="1:3">
+      <c r="A4569" s="7">
+        <v>4567</v>
+      </c>
+      <c r="B4569" s="10">
+        <v>46207</v>
+      </c>
+      <c r="C4569">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4570" spans="1:3">
+      <c r="A4570" s="7">
+        <v>4568</v>
+      </c>
+      <c r="B4570" s="10">
+        <v>46208</v>
+      </c>
+      <c r="C4570">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4571" spans="1:3">
+      <c r="A4571" s="7">
+        <v>4569</v>
+      </c>
+      <c r="B4571" s="10">
+        <v>46209</v>
+      </c>
+      <c r="C4571">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4572" spans="1:3">
+      <c r="A4572" s="7">
+        <v>4570</v>
+      </c>
+      <c r="B4572" s="10">
+        <v>46210</v>
+      </c>
+      <c r="C4572">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4573" spans="1:3">
+      <c r="A4573" s="7">
+        <v>4571</v>
+      </c>
+      <c r="B4573" s="10">
+        <v>46211</v>
+      </c>
+      <c r="C4573">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4574" spans="1:3">
+      <c r="A4574" s="7">
+        <v>4572</v>
+      </c>
+      <c r="B4574" s="10">
+        <v>46212</v>
+      </c>
+      <c r="C4574">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4575" spans="1:3">
+      <c r="A4575" s="7">
+        <v>4573</v>
+      </c>
+      <c r="B4575" s="10">
+        <v>46213</v>
+      </c>
+      <c r="C4575">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4576" spans="1:3">
+      <c r="A4576" s="7">
+        <v>4574</v>
+      </c>
+      <c r="B4576" s="10">
+        <v>46214</v>
+      </c>
+      <c r="C4576">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4577" spans="1:5">
+      <c r="A4577" s="7">
+        <v>4575</v>
+      </c>
+      <c r="B4577" s="10">
+        <v>46215</v>
+      </c>
+      <c r="C4577">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4578" spans="1:5">
+      <c r="A4578" s="7">
+        <v>4576</v>
+      </c>
+      <c r="B4578" s="10">
+        <v>46216</v>
+      </c>
+      <c r="C4578">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4579" spans="1:5">
+      <c r="A4579" s="7">
+        <v>4577</v>
+      </c>
+      <c r="B4579" s="10">
+        <v>46217</v>
+      </c>
+      <c r="C4579">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4580" spans="1:5">
+      <c r="A4580" s="7">
+        <v>4578</v>
+      </c>
+      <c r="B4580" s="10">
+        <v>46218</v>
+      </c>
+      <c r="C4580">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4581" spans="1:5">
+      <c r="A4581" s="7">
+        <v>4579</v>
+      </c>
+      <c r="B4581" s="10">
+        <v>46219</v>
+      </c>
+      <c r="C4581">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4582" spans="1:5">
+      <c r="A4582" s="7">
+        <v>4580</v>
+      </c>
+      <c r="B4582" s="10">
+        <v>46220</v>
+      </c>
+      <c r="C4582">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4583" spans="1:5">
+      <c r="A4583" s="7">
+        <v>4581</v>
+      </c>
+      <c r="B4583" s="10">
+        <v>46221</v>
+      </c>
+      <c r="C4583">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4584" spans="1:5">
+      <c r="A4584" s="7">
+        <v>4582</v>
+      </c>
+      <c r="B4584" s="10">
+        <v>46222</v>
+      </c>
+      <c r="C4584">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4585" spans="1:5">
+      <c r="A4585" s="7">
+        <v>4583</v>
+      </c>
+      <c r="B4585" s="10">
+        <v>46223</v>
+      </c>
+      <c r="C4585">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4586" spans="1:5">
+      <c r="A4586" s="7">
+        <v>4584</v>
+      </c>
+      <c r="B4586" s="10">
+        <v>46224</v>
+      </c>
+      <c r="C4586">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4587" spans="1:5">
+      <c r="A4587" s="7">
+        <v>4585</v>
+      </c>
+      <c r="B4587" s="10">
+        <v>46225</v>
+      </c>
+      <c r="C4587">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4588" spans="1:5">
+      <c r="A4588" s="7">
+        <v>4586</v>
+      </c>
+      <c r="B4588" s="10">
+        <v>46226</v>
+      </c>
+      <c r="C4588">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4589" spans="1:5">
+      <c r="A4589" s="7">
+        <v>4587</v>
+      </c>
+      <c r="B4589" s="10">
+        <v>46227</v>
+      </c>
+      <c r="C4589">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4590" spans="1:5">
+      <c r="A4590" s="7">
+        <v>4588</v>
+      </c>
+      <c r="B4590" s="10">
+        <v>46228</v>
+      </c>
+      <c r="C4590">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4591" spans="1:5">
+      <c r="A4591" s="7">
+        <v>4589</v>
+      </c>
+      <c r="B4591" s="10">
+        <v>46229</v>
+      </c>
+      <c r="C4591">
+        <v>0.8</v>
+      </c>
+      <c r="D4591">
+        <v>1</v>
+      </c>
+      <c r="E4591">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4592" spans="1:5">
+      <c r="A4592" s="7">
+        <v>4590</v>
+      </c>
+      <c r="B4592" s="10">
+        <v>46230</v>
+      </c>
+      <c r="C4592">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4593" spans="1:3">
+      <c r="A4593" s="7">
+        <v>4591</v>
+      </c>
+      <c r="B4593" s="10">
+        <v>46231</v>
+      </c>
+      <c r="C4593">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4594" spans="1:3">
+      <c r="A4594" s="7">
+        <v>4592</v>
+      </c>
+      <c r="B4594" s="10">
+        <v>46232</v>
+      </c>
+      <c r="C4594">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4595" spans="1:3">
+      <c r="A4595" s="7">
+        <v>4593</v>
+      </c>
+      <c r="B4595" s="10">
+        <v>46233</v>
+      </c>
+      <c r="C4595">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4596" spans="1:3">
+      <c r="A4596" s="7">
+        <v>4594</v>
+      </c>
+      <c r="B4596" s="10">
+        <v>46234</v>
+      </c>
+      <c r="C4596">
         <v>0</v>
       </c>
     </row>
@@ -51890,14 +52358,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="42.95" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="43" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="18.85546875" customWidth="1"/>
-    <col min="5" max="5" width="37.140625" customWidth="1"/>
-    <col min="6" max="6" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="11.453125" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" customWidth="1"/>
+    <col min="3" max="3" width="17.1796875" customWidth="1"/>
+    <col min="4" max="4" width="18.81640625" customWidth="1"/>
+    <col min="5" max="5" width="37.1796875" customWidth="1"/>
+    <col min="6" max="6" width="34.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" customHeight="1">
@@ -51934,7 +52402,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="42.95" customHeight="1">
+    <row r="3" spans="1:5" ht="43" customHeight="1">
       <c r="A3" s="2">
         <v>41753</v>
       </c>
@@ -51951,7 +52419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="42.95" customHeight="1">
+    <row r="4" spans="1:5" ht="43" customHeight="1">
       <c r="A4" s="2">
         <v>42001</v>
       </c>
@@ -51968,7 +52436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="42.95" customHeight="1">
+    <row r="5" spans="1:5" ht="43" customHeight="1">
       <c r="A5" s="2">
         <v>42002</v>
       </c>
@@ -51985,7 +52453,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="42.95" customHeight="1">
+    <row r="6" spans="1:5" ht="43" customHeight="1">
       <c r="A6" s="2">
         <v>41643</v>
       </c>
@@ -52002,7 +52470,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="42.95" customHeight="1">
+    <row r="7" spans="1:5" ht="43" customHeight="1">
       <c r="A7" s="2">
         <v>41668</v>
       </c>
@@ -52019,7 +52487,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="42.95" customHeight="1">
+    <row r="8" spans="1:5" ht="43" customHeight="1">
       <c r="A8" s="2">
         <v>41675</v>
       </c>
@@ -52033,7 +52501,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="42.95" customHeight="1">
+    <row r="9" spans="1:5" ht="43" customHeight="1">
       <c r="A9" s="2">
         <v>42234</v>
       </c>
@@ -52047,7 +52515,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="42.95" customHeight="1">
+    <row r="10" spans="1:5" ht="43" customHeight="1">
       <c r="A10" s="2">
         <v>42372</v>
       </c>
@@ -52061,7 +52529,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="42.95" customHeight="1">
+    <row r="11" spans="1:5" ht="43" customHeight="1">
       <c r="A11" s="2">
         <v>42407</v>
       </c>
@@ -52075,7 +52543,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="42.95" customHeight="1">
+    <row r="12" spans="1:5" ht="43" customHeight="1">
       <c r="A12" s="2">
         <v>42415</v>
       </c>
@@ -52089,7 +52557,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="42.95" customHeight="1">
+    <row r="13" spans="1:5" ht="43" customHeight="1">
       <c r="A13" s="2">
         <v>42427</v>
       </c>
@@ -52103,7 +52571,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="42.95" customHeight="1">
+    <row r="14" spans="1:5" ht="43" customHeight="1">
       <c r="A14" s="2">
         <v>42439</v>
       </c>
@@ -52117,7 +52585,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="42.95" customHeight="1">
+    <row r="15" spans="1:5" ht="43" customHeight="1">
       <c r="A15" s="2">
         <v>42444</v>
       </c>
@@ -52131,7 +52599,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="42.95" customHeight="1">
+    <row r="16" spans="1:5" ht="43" customHeight="1">
       <c r="A16" s="2">
         <v>42448</v>
       </c>
@@ -52145,7 +52613,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="42.95" customHeight="1">
+    <row r="17" spans="1:4" ht="43" customHeight="1">
       <c r="A17" s="2">
         <v>42468</v>
       </c>
@@ -52159,7 +52627,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="42.95" customHeight="1">
+    <row r="18" spans="1:4" ht="43" customHeight="1">
       <c r="A18" s="2">
         <v>42480</v>
       </c>
@@ -52173,7 +52641,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="42.95" customHeight="1">
+    <row r="19" spans="1:4" ht="43" customHeight="1">
       <c r="A19" s="2">
         <v>42491</v>
       </c>
@@ -52187,7 +52655,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="42.95" customHeight="1">
+    <row r="20" spans="1:4" ht="43" customHeight="1">
       <c r="A20" s="2">
         <v>42549</v>
       </c>
@@ -52201,7 +52669,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="42.95" customHeight="1">
+    <row r="21" spans="1:4" ht="43" customHeight="1">
       <c r="A21" s="2">
         <v>42550</v>
       </c>
@@ -52215,7 +52683,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="42.95" customHeight="1">
+    <row r="22" spans="1:4" ht="43" customHeight="1">
       <c r="A22" s="2">
         <v>43158</v>
       </c>
@@ -52229,7 +52697,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="42.95" customHeight="1">
+    <row r="23" spans="1:4" ht="43" customHeight="1">
       <c r="A23" s="2">
         <v>43159</v>
       </c>
@@ -52243,7 +52711,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="42.95" customHeight="1">
+    <row r="24" spans="1:4" ht="43" customHeight="1">
       <c r="A24" s="2">
         <v>43160</v>
       </c>
@@ -52257,7 +52725,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="42.95" customHeight="1">
+    <row r="25" spans="1:4" ht="43" customHeight="1">
       <c r="A25" s="2">
         <v>43161</v>
       </c>
@@ -52271,7 +52739,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="42.95" customHeight="1">
+    <row r="26" spans="1:4" ht="43" customHeight="1">
       <c r="A26" s="2">
         <v>43358</v>
       </c>
@@ -52285,7 +52753,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="42.95" customHeight="1">
+    <row r="27" spans="1:4" ht="43" customHeight="1">
       <c r="A27" s="2">
         <v>43360</v>
       </c>
@@ -52299,7 +52767,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="42.95" customHeight="1">
+    <row r="28" spans="1:4" ht="43" customHeight="1">
       <c r="A28" s="2">
         <v>43413</v>
       </c>
@@ -52313,7 +52781,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="42.95" customHeight="1">
+    <row r="29" spans="1:4" ht="43" customHeight="1">
       <c r="A29" s="2">
         <v>43418</v>
       </c>
@@ -52327,7 +52795,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="42.95" customHeight="1">
+    <row r="30" spans="1:4" ht="43" customHeight="1">
       <c r="A30" s="2">
         <v>43430</v>
       </c>
@@ -52341,7 +52809,7 @@
         <v>45949</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="42.95" customHeight="1">
+    <row r="31" spans="1:4" ht="43" customHeight="1">
       <c r="A31" s="2">
         <v>43654</v>
       </c>

--- a/data/daily_manual_rain_gage_data.xlsx
+++ b/data/daily_manual_rain_gage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eiven\O2 Cloud\git\app-secar_meteo_data\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC7B50B-F022-4715-B256-6BF0393E6406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF109269-3C21-4191-A8C3-21D4E7882BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -531,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4596"/>
+  <dimension ref="A1:E4611"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -52347,6 +52347,171 @@
         <v>46234</v>
       </c>
       <c r="C4596">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4597" spans="1:3">
+      <c r="A4597" s="7">
+        <v>4595</v>
+      </c>
+      <c r="B4597" s="10">
+        <v>46235</v>
+      </c>
+      <c r="C4597">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4598" spans="1:3">
+      <c r="A4598" s="7">
+        <v>4596</v>
+      </c>
+      <c r="B4598" s="10">
+        <v>46236</v>
+      </c>
+      <c r="C4598">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4599" spans="1:3">
+      <c r="A4599" s="7">
+        <v>4597</v>
+      </c>
+      <c r="B4599" s="10">
+        <v>46237</v>
+      </c>
+      <c r="C4599">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4600" spans="1:3">
+      <c r="A4600" s="7">
+        <v>4598</v>
+      </c>
+      <c r="B4600" s="10">
+        <v>46238</v>
+      </c>
+      <c r="C4600">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4601" spans="1:3">
+      <c r="A4601" s="7">
+        <v>4599</v>
+      </c>
+      <c r="B4601" s="10">
+        <v>46239</v>
+      </c>
+      <c r="C4601">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4602" spans="1:3">
+      <c r="A4602" s="7">
+        <v>4600</v>
+      </c>
+      <c r="B4602" s="10">
+        <v>46240</v>
+      </c>
+      <c r="C4602">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4603" spans="1:3">
+      <c r="A4603" s="7">
+        <v>4601</v>
+      </c>
+      <c r="B4603" s="10">
+        <v>46241</v>
+      </c>
+      <c r="C4603">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4604" spans="1:3">
+      <c r="A4604" s="7">
+        <v>4602</v>
+      </c>
+      <c r="B4604" s="10">
+        <v>46242</v>
+      </c>
+      <c r="C4604">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4605" spans="1:3">
+      <c r="A4605" s="7">
+        <v>4603</v>
+      </c>
+      <c r="B4605" s="10">
+        <v>46243</v>
+      </c>
+      <c r="C4605">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4606" spans="1:3">
+      <c r="A4606" s="7">
+        <v>4604</v>
+      </c>
+      <c r="B4606" s="10">
+        <v>46244</v>
+      </c>
+      <c r="C4606">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4607" spans="1:3">
+      <c r="A4607" s="7">
+        <v>4605</v>
+      </c>
+      <c r="B4607" s="10">
+        <v>46245</v>
+      </c>
+      <c r="C4607">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4608" spans="1:3">
+      <c r="A4608" s="7">
+        <v>4606</v>
+      </c>
+      <c r="B4608" s="10">
+        <v>46246</v>
+      </c>
+      <c r="C4608">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4609" spans="1:3">
+      <c r="A4609" s="7">
+        <v>4607</v>
+      </c>
+      <c r="B4609" s="10">
+        <v>46247</v>
+      </c>
+      <c r="C4609">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4610" spans="1:3">
+      <c r="A4610" s="7">
+        <v>4608</v>
+      </c>
+      <c r="B4610" s="10">
+        <v>46248</v>
+      </c>
+      <c r="C4610">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4611" spans="1:3">
+      <c r="A4611" s="7">
+        <v>4609</v>
+      </c>
+      <c r="B4611" s="10">
+        <v>46249</v>
+      </c>
+      <c r="C4611">
         <v>0</v>
       </c>
     </row>
